--- a/data/trans_orig/IP1009-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1009-Edad-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103897</t>
+          <t>103922</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>224989</t>
+          <t>225316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>249911</t>
+          <t>250018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>503046</t>
+          <t>503159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136980</t>
+          <t>138123</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265641</t>
+          <t>265656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201197</t>
+          <t>201836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>395564</t>
+          <t>395936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>677318</t>
+          <t>676771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>717142</t>
+          <t>717149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>722024</t>
+          <t>722023</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1396483</t>
+          <t>1396631</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402587</t>
+          <t>1402636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155421</t>
+          <t>155471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309842</t>
+          <t>310133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166179</t>
+          <t>166813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344731</t>
+          <t>344739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>701906</t>
+          <t>702348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>745026</t>
+          <t>744680</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1450550</t>
+          <t>1450498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1455070</t>
+          <t>1454453</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,96%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>205446</t>
+          <t>205275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>210062</t>
+          <t>210064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>254741</t>
+          <t>254733</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>462348</t>
+          <t>462707</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>467914</t>
+          <t>467975</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168846</t>
+          <t>169388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168421</t>
+          <t>168293</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>173463</t>
+          <t>173461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340278</t>
+          <t>340775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346619</t>
+          <t>346627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>697209</t>
+          <t>698002</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>703602</t>
+          <t>703765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>738112</t>
+          <t>737975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744170</t>
+          <t>744176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1438717</t>
+          <t>1438793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1446534</t>
+          <t>1446649</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1009-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1009-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>448</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2249</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2496</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2235</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>105723</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>103922</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>103675</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,58%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>343</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>225316</t>
+          <t>225174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>634</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3187</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3604</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3802</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>252571</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>250018</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>249601</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>760</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>503159</t>
+          <t>503780</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3397</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>679</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3392</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3407</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140836</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>138118</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140836</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>138123</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265656</t>
+          <t>265660</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1393</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4207</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1393</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4213</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4881</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1393</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4210</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>204656</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>201842</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>204656</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>201836</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>395936</t>
+          <t>395265</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5550</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1081</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4250</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3695</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5551</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>720628</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>717150</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>722021</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679940</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>676771</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>677326</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,84%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>720628</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>717149</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>722023</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2099</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1396631</t>
+          <t>1397099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402636</t>
+          <t>1402639</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3125,47 +3125,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3760</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>619</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3546</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157952</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154811</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157952</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>155471</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>310133</t>
+          <t>309859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,92 +3698,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4524</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5165</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>170034</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>166813</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>166172</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,24%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,99%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>503</t>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344739</t>
+          <t>344769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,92 +4041,92 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3197</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4580</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4504</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1922</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>619</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3462</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1922</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>747523</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>744945</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>705625</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>702348</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>702424</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,82%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>747523</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>744680</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2081</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1450498</t>
+          <t>1449877</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454453</t>
+          <t>1454451</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3305</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1813</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5242</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5476</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,22%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3328</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>257398</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>254756</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>208704</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>205275</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>210064</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>205041</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>210063</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,14%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,78%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>257398</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>254733</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>708</t>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>462707</t>
+          <t>462042</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>467975</t>
+          <t>467914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5676</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>772</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3913</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5755</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>172009</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>168372</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>173464</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>172529</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>169388</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>170089</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,55%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>172009</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>168293</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>173461</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,69%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>477</t>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340775</t>
+          <t>340760</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346627</t>
+          <t>346620</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5993,102 +5993,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>2585</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6369</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6577</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6869</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>5287</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>10690</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>5287</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2566</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>10422</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -6101,107 +6101,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742142</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>737923</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744128</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1057</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>701786</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>698002</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>703765</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>697794</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>703617</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742142</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>737975</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744176</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,89%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1443928</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1438525</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1446743</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1443928</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1438793</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1446649</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
